--- a/data/demo/Запад бригады.xlsx
+++ b/data/demo/Запад бригады.xlsx
@@ -464,7 +464,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>г Москва, вн.тер.г. муниципальный округ Крылатское, б-р.Осенний, д. 18 к 2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -482,7 +486,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Веерная, д. 3 к 5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -500,7 +508,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Клочкова, д. 8</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -518,7 +530,11 @@
           <t>Ремонт, Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Город Москва, наб.Шелепихинская, д. 4с1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,7 +552,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Кравченко, д. 16 к 1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -554,7 +574,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Нежинская, д. 1 к 4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,7 +596,11 @@
           <t>Подключение и дозаказ, Аварии</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Большая Очаковская, д. 12 к 5</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -590,7 +618,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Усачёва, д. 29 к 3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,7 +640,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Город Москва, пр-кт.Кутузовский, д. 69 к 5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -626,7 +662,11 @@
           <t>Ремонт, Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Город Москва, ш.Очаковское, д. 8 к 2</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -644,7 +684,11 @@
           <t>Подключение и дозаказ</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Город Москва, ул.Крылатские Холмы, д. 32 к 2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
